--- a/model/experiment_results.xlsx
+++ b/model/experiment_results.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-25 15:12:40</t>
+          <t>2026-03-26 12:22:54</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">

--- a/model/experiment_results.xlsx
+++ b/model/experiment_results.xlsx
@@ -510,7 +510,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>2026-03-26 12:22:54</t>
+          <t>2026-03-27 11:21:18</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
